--- a/Gokavi_Template_Classification.xlsx
+++ b/Gokavi_Template_Classification.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Message Flow" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Template Classification" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Meta API JSON" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Change Log (2026-09)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +56,13 @@
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +102,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -123,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -161,6 +172,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -526,1064 +548,989 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Step Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Message / Question Text</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Response Options</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Choose language</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Welcome to Gokavi IVF &amp; Fertility Centre. Please choose your language.</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>English / ಕನ್ನಡ (Kannada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Before we continue, please confirm you're okay with the following, all over WhatsApp: 1) Receiving appointment, medication, and cycle updates... 2) processing your health data... 3) Receiving treatment-related messages... Do you agree to all of the above?</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Before we continue, please confirm you're okay with the following, all over WhatsApp: 1) Receiving appointment, medication, and cycle updates 2) processing your health data 3) Receiving treatment-related messages. Do you agree to all of the above?</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
         <is>
           <t>I agree / I don't agree</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Decline path</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Understood. Without this consent we're unable to continue over WhatsApp...</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>Thank you. What's your full name?</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>Free text</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Patient ID</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Do you already have a patient ID from the clinic?</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Enter patient ID / New patient</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Which city or place are you located in?</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ID entry (if Enter tapped)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Please type your patient ID.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Presenting problem</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>What is the problem you'd like to discuss?</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>List (10): Infertility / Low sperm count / Zero sperm count (Azoospermia) / Fibroid / Ovarian cyst / Endometriosis / Heavy bleeding / Painful periods / PCOS / PCOD / Irregular periods</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Onboarding complete</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Thank you! Our clinic will connect with you shortly.</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Which department would you like to book?</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Doctor</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>IVF continuity of care matters — pick the doctor you'd like to continue with.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Pick a week to see available days:</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Pick a date:</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Pick a 1-hour slot:</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Confirmation</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Thanks — we've received your booking request ({date/time} preferred). Our team will confirm your exact appointment slot shortly.</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Booking</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>ART Act reminder</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Reminder: before your treatment begins, India's ART Act 2021 requires you to complete our clinic's informed-consent process in person...</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Main menu</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>{Greeting}. What would you like to do?</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Book Follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>My Appointment / Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule / Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Medication Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Refer a Friend</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Ask a Question</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Talk to Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Appointment options</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Your appointment: {date/time}. What would you like to do?</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule / Cancel appointment</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule - week</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Pick a week to see available days:</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule - date</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Pick a date:</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule - time</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Pick a 1-hour slot:</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>List</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Cancel (normal)</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Your appointment has been cancelled. Reply BOOK any time to schedule a new one.</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Reschedule/Cancel</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Cancel (cycle-critical)</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>This is a time-sensitive part of your cycle, so our care team will call you to confirm cancelling this appointment rather than cancelling it automatically.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Identity verification</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Report access</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Your {test} report is ready. For your security, please confirm your date of birth (DD-MM-YYYY) to view it.</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Free text</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Partner link</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Add a partner/spouse contact for shared updates?</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Yes / Not now</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Partner phone (if Yes)</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Please share your partner's WhatsApp number (with country code).</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Identity verification</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Care plan access</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Before we share your consultation summary and care plan, please confirm your date of birth (DD-MM-YYYY)...</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Free text</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Reason</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>What brings you to us?</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>IVF treatment / General consultation / Other, not sure yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Prior attempts</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Have you tried IVF or fertility treatment before?</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>First time trying / 1 prior attempt / 2 or more prior attempts</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Which city are you located in?</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Free text</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Which department would you like to book?</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Doctor</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>IVF continuity of care matters — pick the doctor you'd like to continue with.</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Week</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Pick a week to see available days:</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Pick a date:</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Pick a 1-hour slot:</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Confirmation</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Thanks — we've received your booking request ({date/time} preferred). Our team will confirm your exact appointment slot shortly.</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>ART Act reminder</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Reminder: before your treatment begins, India's ART Act 2021 requires you to complete our clinic's informed-consent process in person...</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Main menu</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>{Greeting}. What would you like to do?</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Book Follow-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>My Appointment / Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Reschedule / Cancel</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Medication Schedule</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Refer a Friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Ask a Question</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Existing-patient menu</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Main menu (cont.)</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>Talk to Staff</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Appointment options</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>Your appointment: {date/time}. What would you like to do?</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>Reschedule / Cancel appointment</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Reschedule - week</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Pick a week to see available days:</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Reschedule - date</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>Pick a date:</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Reschedule - time</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Pick a 1-hour slot:</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Cancel (normal)</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>Your appointment has been cancelled. Reply BOOK any time to schedule a new one.</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Cancel (cycle-critical)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>This is a time-sensitive part of your cycle, so our care team will call you to confirm cancelling this appointment rather than cancelling it automatically.</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Post-OPU: pain</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>How would you rate your pain right now?</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>mild / moderate / severe</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Identity verification</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Report access</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Your {test} report is ready. For your security, please confirm your date of birth (DD-MM-YYYY) to view it.</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Free text</t>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Post-OPU: bleeding</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Any vaginal bleeding since the procedure?</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>none / light spotting / heavy-soaking pad</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Identity verification</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Care plan access</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>Before we share your consultation summary and care plan, please confirm your date of birth (DD-MM-YYYY)...</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Free text</t>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Post-OPU: breathlessness</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Any breathlessness or difficulty breathing?</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>no / yes</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Post-procedure symptom check-ins</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Post-OPU: pain</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>How would you rate your pain right now?</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>Post-OPU: abdomen</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Is your abdomen significantly swollen or distended?</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>no / slightly / severely</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Post-transfer: pain</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Any cramping or pain right now?</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>mild / moderate / severe</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>Post-procedure symptom check-ins</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Post-OPU: bleeding</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Any vaginal bleeding since the procedure?</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>none / light spotting / heavy-soaking pad</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Post-transfer: bleeding</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Any bleeding since the transfer?</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>none / light spotting / heavy bleeding</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>Post-procedure symptom check-ins</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Post-OPU: breathlessness</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>Any breathlessness or difficulty breathing?</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Post-transfer: breathlessness</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Any breathlessness?</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>no / yes</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Post-OPU: abdomen</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Is your abdomen significantly swollen or distended?</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>no / slightly / severely</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="15" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Post-transfer: pain</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Any cramping or pain right now?</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>mild / moderate / severe</t>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Feedback &amp; testimonial</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Positive outcome (NPS)</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>...on a scale of 0-10, how likely are you to recommend us to someone on a similar journey?</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>0-10 scale</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="15" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Post-transfer: bleeding</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>Any bleeding since the transfer?</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>none / light spotting / heavy bleeding</t>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Feedback &amp; testimonial</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Negative outcome</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>...Would you be open to sharing a few thoughts?</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Yes I'll share / Not right now</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Post-transfer: breathlessness</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>Any breathlessness?</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>no / yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>Feedback &amp; testimonial</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Positive outcome (NPS)</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>...on a scale of 0-10, how likely are you to recommend us to someone on a similar journey?</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>0-10 scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Feedback &amp; testimonial</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Negative outcome</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>...Would you be open to sharing a few thoughts?</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Yes I'll share / Not right now</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Feedback &amp; testimonial</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Testimonial ask</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>...would you be open to sharing your story as a testimonial to help other patients considering treatment?</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Yes, happy to / No thanks</t>
         </is>
@@ -1600,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1662,317 +1609,317 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>Choose language</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>SESSION_REPLY</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>Welcome to Gokavi IVF &amp; Fertility Centre. Please choose your language.</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>Quick Reply: English / ಕನ್ನಡ</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>NEW STEP (added since the last version of this document). Bot's own first reply to the patient's inbound message — same session, no template needed. Every subsequent question is shown in whichever language is picked here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>Consent</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
         <is>
           <t>Before we continue, please confirm you're okay with the following, all over WhatsApp: 1) Receiving appointment, medication, and cycle updates 2) processing your health data 3) Receiving treatment-related messages. Do you agree to all of the above?</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>Quick Reply: I agree / I don't agree</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>Sent as the bot's reply to the patient's own first inbound message, which opens the 24h customer-service window.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Same session. Recorded internally as three distinct, timestamped, versioned consent rows (DPDP Act 2023), still shown to the patient as one combined question.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>Decline path</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>Understood. Without this consent we're unable to continue over WhatsApp...</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>Immediate reply to the 'I don't agree' tap, same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Immediate reply to the 'I don't agree' tap. Onboarding ends here if declined — no further questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t>Thank you. What's your full name?</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Free text</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Same session.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Patient ID</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>Do you already have a patient ID from the clinic?</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="inlineStr">
-        <is>
-          <t>Enter patient ID / New patient</t>
-        </is>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Which city or place are you located in?</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>RENAMED + MOVED (previously 'City', asked later after the removed reason/prior-attempts questions). Open-ended, no fixed answer set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>ID entry (if Enter tapped)</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Presenting problem</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>Please type your patient ID.</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>Free text</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>What is the problem you'd like to discuss?</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>Interactive List (10 rows): Infertility / Low sperm count / Zero sperm count (Azoospermia) / Fibroid / Ovarian cyst / Endometriosis / Heavy bleeding / Painful periods / PCOS / PCOD / Irregular periods</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>REPLACES the old 3-option 'Reason' question AND the old 3-option 'Prior attempts' question — both removed. Fixed list per client's exact 10 options, not free text, so every answer is one of a known, analyzable set. "Zero sperm count (Azoospermia)" is split as row title "Zero sperm count" + row description "Azoospermia" to fit Meta's 24-character row-title limit; the full text is still what's stored on the patient record. Fills a WhatsApp interactive list's 10-row-per-section limit exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Onboarding</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Partner link</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Onboarding complete</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>Add a partner/spouse contact for shared updates?</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>Yes / Not now</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Onboarding</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Partner phone (if Yes)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>SESSION_REPLY</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Please share your partner's WhatsApp number (with country code).</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>Free text</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Thank you! Our clinic will connect with you shortly.</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>NEW STEP, replaces the old immediate hand-off into Booking (old step 11 'Department'). Per explicit client decision, onboarding no longer flows into self-service slot booking — a staff member follows up and books manually instead. The Booking section below (department/doctor/week/date/time) still exists in the bot code and is still used for reschedule/cancel and staff-side booking, but a new lead completing onboarding no longer lands there automatically.</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1929,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Booking</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2007,17 +1954,17 @@
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>What brings you to us?</t>
+          <t>Which department would you like to book?</t>
         </is>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>IVF treatment / General consultation / Other, not sure yet</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Same session.</t>
+          <t>Same active session (booking flow continues from onboarding or a 'Book' menu tap).</t>
         </is>
       </c>
     </row>
@@ -2027,12 +1974,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Booking</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Prior attempts</t>
+          <t>Doctor</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -2052,12 +1999,12 @@
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Have you tried IVF or fertility treatment before?</t>
+          <t>IVF continuity of care matters — pick the doctor you'd like to continue with.</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>First time trying / 1 prior attempt / 2 or more prior attempts</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -2072,12 +2019,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Booking</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Week</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -2097,17 +2044,17 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Which city are you located in?</t>
+          <t>Pick a week to see available days:</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Free text</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Same session, completes onboarding.</t>
+          <t>Same session.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2069,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -2142,7 +2089,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Which department would you like to book?</t>
+          <t>Pick a date:</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -2152,7 +2099,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Same active session (booking flow continues from onboarding or a 'Book' menu tap).</t>
+          <t>Same session.</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2114,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -2187,7 +2134,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>IVF continuity of care matters — pick the doctor you'd like to continue with.</t>
+          <t>Pick a 1-hour slot:</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -2212,7 +2159,7 @@
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>Confirmation</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
@@ -2232,62 +2179,62 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Pick a week to see available days:</t>
+          <t>Thanks — we've received your booking request ({date/time} preferred). Our team will confirm your exact appointment slot shortly.</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>Same session.</t>
+          <t>Immediate ack in the same session. NOTE: the *actual* human-confirmed appointment message this text promises ('Our team will confirm shortly') is not one of the 42 rows in the source sheet, but in a real deployment that follow-up is sent by staff after manual review and may land hours later, outside the 24h window — it would need its own TEMPLATE_REQUIRED entry (e.g. appointment_confirmed) not currently specified. Flagging as a gap for you to add if staff confirmation isn't instant.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Booking</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>SESSION_REPLY</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Pick a date:</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>ART Act reminder</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>TEMPLATE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>art_act_consent_reminder</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>UTILITY</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Reminder: before your treatment begins, India's ART Act 2021 requires you to complete an in-person informed-consent process at our clinic. Please visit us before your scheduled appointment on {{1}}, or reply to this message and we'll help you arrange a time.</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Quick Reply: 'Help me arrange a visit'  |  Call button: 'Call the clinic' (phone_number)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Classified TEMPLATE_REQUIRED, not a session reply: 'Reminder' framing plus the compliance purpose imply this is sent as a standalone nudge closer to the treatment date (which may be days/weeks after the booking session ended), not chained immediately onto step 16. Category is clearly Utility (legal/compliance notice tied to an already-booked service) — not ambiguous. Source text ended in '...' — body completed to a submittable sentence.</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2244,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Booking</t>
+          <t>Existing-patient menu</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Main menu</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
@@ -2322,17 +2269,17 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Pick a 1-hour slot:</t>
+          <t>{Greeting}. What would you like to do?</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>Book Follow-up / My Appointment / Report / Reschedule / Cancel / Medication Schedule / Refer a Friend / Ask a Question / Talk to Staff</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Same session.</t>
+          <t>Reply to the returning patient's own inbound message (e.g. 'Hi'), opening the session.</t>
         </is>
       </c>
     </row>
@@ -2342,17 +2289,17 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Booking</t>
+          <t>Existing-patient menu</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Confirmation</t>
+          <t>Main menu (cont.)</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>SESSION_REPLY</t>
+          <t>SESSION_REPLY (N/A — same message as #18)</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -2367,62 +2314,62 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>Thanks — we've received your booking request ({date/time} preferred). Our team will confirm your exact appointment slot shortly.</t>
+          <t>(same message as step 18)</t>
         </is>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>My Appointment / Report</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Immediate ack in the same session. NOTE: the *actual* human-confirmed appointment message this text promises ('Our team will confirm shortly') is not one of the 42 rows in the source sheet, but in a real deployment that follow-up is sent by staff after manual review and may land hours later, outside the 24h window — it would need its own TEMPLATE_REQUIRED entry (e.g. appointment_confirmed) not currently specified. Flagging as a gap for you to add if staff confirmation isn't instant.</t>
+          <t>Not a separate message — one option in the step-18 interactive list.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>Booking</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>ART Act reminder</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>TEMPLATE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>art_act_consent_reminder</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>UTILITY</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>Reminder: before your treatment begins, India's ART Act 2021 requires you to complete an in-person informed-consent process at our clinic. Please visit us before your scheduled appointment on {{1}}, or reply to this message and we'll help you arrange a time.</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>Quick Reply: 'Help me arrange a visit'  |  Call button: 'Call the clinic' (phone_number)</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>Classified TEMPLATE_REQUIRED, not a session reply: 'Reminder' framing plus the compliance purpose imply this is sent as a standalone nudge closer to the treatment date (which may be days/weeks after the booking session ended), not chained immediately onto step 16. Category is clearly Utility (legal/compliance notice tied to an already-booked service) — not ambiguous. Source text ended in '...' — body completed to a submittable sentence.</t>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Existing-patient menu</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Main menu (cont.)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>SESSION_REPLY (N/A — same message as #18)</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>(same message as step 18)</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Reschedule / Cancel</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>Not a separate message — one option in the step-18 interactive list.</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2384,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Main menu</t>
+          <t>Main menu (cont.)</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>SESSION_REPLY</t>
+          <t>SESSION_REPLY (N/A — same message as #18)</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -2457,17 +2404,17 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>{Greeting}. What would you like to do?</t>
+          <t>(same message as step 18)</t>
         </is>
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Book Follow-up / My Appointment / Report / Reschedule / Cancel / Medication Schedule / Refer a Friend / Ask a Question / Talk to Staff</t>
+          <t>Medication Schedule</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>Reply to the returning patient's own inbound message (e.g. 'Hi'), opening the session.</t>
+          <t>Not a separate message — one option in the step-18 interactive list.</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2454,7 @@
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>My Appointment / Report</t>
+          <t>Refer a Friend</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -2552,7 +2499,7 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Reschedule / Cancel</t>
+          <t>Ask a Question</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -2597,7 +2544,7 @@
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Medication Schedule</t>
+          <t>Talk to Staff</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -2612,17 +2559,17 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Existing-patient menu</t>
+          <t>Reschedule/Cancel</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Main menu (cont.)</t>
+          <t>Appointment options</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>SESSION_REPLY (N/A — same message as #18)</t>
+          <t>SESSION_REPLY</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -2637,17 +2584,17 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>(same message as step 18)</t>
+          <t>Your appointment: {date/time}. What would you like to do?</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
-          <t>Refer a Friend</t>
+          <t>Reschedule / Cancel appointment</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Not a separate message — one option in the step-18 interactive list.</t>
+          <t>Reply to 'Reschedule / Cancel' tap from step 18/20, same session.</t>
         </is>
       </c>
     </row>
@@ -2657,17 +2604,17 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Existing-patient menu</t>
+          <t>Reschedule/Cancel</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Main menu (cont.)</t>
+          <t>Reschedule - week</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>SESSION_REPLY (N/A — same message as #18)</t>
+          <t>SESSION_REPLY</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -2682,17 +2629,17 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>(same message as step 18)</t>
+          <t>Pick a week to see available days:</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Ask a Question</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>Not a separate message — one option in the step-18 interactive list.</t>
+          <t>Same session.</t>
         </is>
       </c>
     </row>
@@ -2702,17 +2649,17 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Existing-patient menu</t>
+          <t>Reschedule/Cancel</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Main menu (cont.)</t>
+          <t>Reschedule - date</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>SESSION_REPLY (N/A — same message as #18)</t>
+          <t>SESSION_REPLY</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -2727,17 +2674,17 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>(same message as step 18)</t>
+          <t>Pick a date:</t>
         </is>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>Talk to Staff</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Not a separate message — one option in the step-18 interactive list.</t>
+          <t>Same session.</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2699,7 @@
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Appointment options</t>
+          <t>Reschedule - time</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -2772,17 +2719,17 @@
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>Your appointment: {date/time}. What would you like to do?</t>
+          <t>Pick a 1-hour slot:</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Reschedule / Cancel appointment</t>
+          <t>List</t>
         </is>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>Reply to 'Reschedule / Cancel' tap from step 18/20, same session.</t>
+          <t>Same session.</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2744,7 @@
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Reschedule - week</t>
+          <t>Cancel (normal)</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
@@ -2817,17 +2764,17 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>Pick a week to see available days:</t>
+          <t>Your appointment has been cancelled. Reply BOOK any time to schedule a new one.</t>
         </is>
       </c>
       <c r="H27" s="9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>Same session.</t>
+          <t>Immediate reply to the 'Cancel appointment' tap, same session.</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2789,7 @@
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Reschedule - date</t>
+          <t>Cancel (cycle-critical)</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -2862,332 +2809,332 @@
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Pick a date:</t>
+          <t>This is a time-sensitive part of your cycle, so our care team will call you to confirm cancelling this appointment rather than cancelling it automatically.</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>List</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>Same session.</t>
+          <t>Immediate reply to the cancel tap (the actual phone call happens off-WhatsApp), same session.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Reschedule - time</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Identity verification</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Report access</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>TEMPLATE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>report_ready_verify_dob</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>UTILITY</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Hi {{1}}, your {{2}} report is ready. For your security, please reply with your date of birth (DD-MM-YYYY) to view it.</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>None — expects a free-text DOB reply</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Proactive: triggered when the lab uploads a result, not by any inbound patient message, so it's outside any open session. Utility — pure account/security notification about an already-ordered test, not promotional. Source text ended in '...' — completed to full sentence; added {{1}} name and {{2}} test-name variables per the flow's own '{test}' placeholder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Identity verification</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Care plan access</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>TEMPLATE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>careplan_ready_verify_dob</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>UTILITY</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Hi {{1}}, your consultation summary and care plan from Dr. {{2}} are ready. For your security, please reply with your date of birth (DD-MM-YYYY) before we share them.</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>None — expects a free-text DOB reply</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Proactive: triggered when the doctor finalizes the consult note, not by an inbound message. Utility (account/security gate on an already-completed consult). Source text ended in '...' — completed to full sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Post-OPU: pain</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>TEMPLATE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>post_opu_checkin_pain</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>UTILITY</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Hi {{1}}, this is Gokavi Hospital checking in after your OPU procedure on {{2}}. How would you rate your pain right now?</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Quick Reply: Mild / Moderate / Severe</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>This is the FIRST message of the post-OPU check-in — it's a scheduled, clinic-initiated check some hours after the procedure, not a reply to an inbound message, so it needs a template. Utility — direct post-op safety monitoring for a specific procedure already performed, not promotional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Post-OPU: bleeding</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>Pick a 1-hour slot:</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>List</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>Same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Cancel (normal)</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Any vaginal bleeding since the procedure?</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>none / light spotting / heavy-soaking pad</t>
+        </is>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>Asked immediately after the patient answers step 33 — happens inside the 24h session that step 33's template opened, so no template is needed for this or the remaining questions in the same check-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Post-OPU: breathlessness</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>Your appointment has been cancelled. Reply BOOK any time to schedule a new one.</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>Immediate reply to the 'Cancel appointment' tap, same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Reschedule/Cancel</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Cancel (cycle-critical)</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Any breathlessness or difficulty breathing?</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>no / yes</t>
+        </is>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>Same session opened by step 33 (red-flag symptom check).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Post-OPU: abdomen</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>SESSION_REPLY</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>This is a time-sensitive part of your cycle, so our care team will call you to confirm cancelling this appointment rather than cancelling it automatically.</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>Immediate reply to the cancel tap (the actual phone call happens off-WhatsApp), same session.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Identity verification</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Report access</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Is your abdomen significantly swollen or distended?</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>no / slightly / severely</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>Same session opened by step 33 (OHSS red-flag check).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Post-procedure symptom check-ins</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Post-transfer: pain</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>TEMPLATE_REQUIRED</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>report_ready_verify_dob</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>post_transfer_checkin_pain</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>UTILITY</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>Hi {{1}}, your {{2}} report is ready. For your security, please reply with your date of birth (DD-MM-YYYY) to view it.</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>None — expects a free-text DOB reply</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Proactive: triggered when the lab uploads a result, not by any inbound patient message, so it's outside any open session. Utility — pure account/security notification about an already-ordered test, not promotional. Source text ended in '...' — completed to full sentence; added {{1}} name and {{2}} test-name variables per the flow's own '{test}' placeholder.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Identity verification</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Care plan access</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>TEMPLATE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>careplan_ready_verify_dob</t>
-        </is>
-      </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>UTILITY</t>
-        </is>
-      </c>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>Hi {{1}}, your consultation summary and care plan from Dr. {{2}} are ready. For your security, please reply with your date of birth (DD-MM-YYYY) before we share them.</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>None — expects a free-text DOB reply</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>Proactive: triggered when the doctor finalizes the consult note, not by an inbound message. Utility (account/security gate on an already-completed consult). Source text ended in '...' — completed to full sentence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Post-OPU: pain</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>TEMPLATE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>post_opu_checkin_pain</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>UTILITY</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>Hi {{1}}, this is Gokavi Hospital checking in after your OPU procedure on {{2}}. How would you rate your pain right now?</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Hi {{1}}, this is Gokavi Hospital checking in after your embryo transfer on {{2}}. Any cramping or pain right now?</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Quick Reply: Mild / Moderate / Severe</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>This is the FIRST message of the post-OPU check-in — it's a scheduled, clinic-initiated check some hours after the procedure, not a reply to an inbound message, so it needs a template. Utility — direct post-op safety monitoring for a specific procedure already performed, not promotional.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Post-procedure symptom check-ins</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Post-OPU: bleeding</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>SESSION_REPLY</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>Any vaginal bleeding since the procedure?</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>none / light spotting / heavy-soaking pad</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>Asked immediately after the patient answers step 33 — happens inside the 24h session that step 33's template opened, so no template is needed for this or the remaining questions in the same check-in.</t>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>FIRST message of the post-transfer check-in, scheduled proactively after the transfer procedure — same reasoning as step 33. Utility.</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3149,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Post-OPU: breathlessness</t>
+          <t>Post-transfer: bleeding</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -3222,17 +3169,17 @@
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>Any breathlessness or difficulty breathing?</t>
+          <t>Any bleeding since the transfer?</t>
         </is>
       </c>
       <c r="H36" s="9" t="inlineStr">
         <is>
-          <t>no / yes</t>
+          <t>none / light spotting / heavy bleeding</t>
         </is>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>Same session opened by step 33 (red-flag symptom check).</t>
+          <t>Same session opened by step 37.</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3194,7 @@
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Post-OPU: abdomen</t>
+          <t>Post-transfer: breathlessness</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -3267,17 +3214,17 @@
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>Is your abdomen significantly swollen or distended?</t>
+          <t>Any breathlessness?</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
         <is>
-          <t>no / slightly / severely</t>
+          <t>no / yes</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
-          <t>Same session opened by step 33 (OHSS red-flag check).</t>
+          <t>Same session opened by step 37.</t>
         </is>
       </c>
     </row>
@@ -3287,12 +3234,12 @@
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>Post-procedure symptom check-ins</t>
+          <t>Feedback &amp; testimonial</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Post-transfer: pain</t>
+          <t>Positive outcome (NPS)</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -3302,27 +3249,27 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>post_transfer_checkin_pain</t>
+          <t>treatment_feedback_nps_survey</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>UTILITY</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>Hi {{1}}, this is Gokavi Hospital checking in after your embryo transfer on {{2}}. Any cramping or pain right now?</t>
+          <t>Hi {{1}}, thank you for trusting Gokavi Hospital with your care. On a scale of 0-10, how likely are you to recommend us to someone on a similar journey? Just reply with a number.</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr">
         <is>
-          <t>Quick Reply: Mild / Moderate / Severe</t>
+          <t>Quick Reply: 'Stop promotional messages' (Meta opt-out requirement for Marketing templates)</t>
         </is>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>FIRST message of the post-transfer check-in, scheduled proactively after the transfer procedure — same reasoning as step 33. Utility.</t>
+          <t>CONFIRMED WITH USER: classified Marketing, not Utility. Sent proactively, well outside any open session, and is a satisfaction/NPS survey — Meta's own template guidelines list 'invitations to fill out a survey' as a Marketing example. Marketing templates cost more, are subject to Meta's marketing message-limit tiers, and need an opt-out affordance (added a Quick Reply button) — verify Meta's current opt-out requirement at submission time, as policy has changed before.</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3279,12 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Post-procedure symptom check-ins</t>
+          <t>Feedback &amp; testimonial</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Post-transfer: bleeding</t>
+          <t>Negative outcome</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -3357,17 +3304,17 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Any bleeding since the transfer?</t>
+          <t>...Would you be open to sharing a few thoughts?</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>none / light spotting / heavy bleeding</t>
+          <t>Yes I'll share / Not right now</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>Same session opened by step 37.</t>
+          <t>Branch reply triggered immediately by the patient's low NPS score in step 40 — inside the session that step 40's template opened.</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3324,12 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Post-procedure symptom check-ins</t>
+          <t>Feedback &amp; testimonial</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Post-transfer: breathlessness</t>
+          <t>Testimonial ask</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -3402,150 +3349,15 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>Any breathlessness?</t>
+          <t>...would you be open to sharing your story as a testimonial to help other patients considering treatment?</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>no / yes</t>
+          <t>Yes, happy to / No thanks</t>
         </is>
       </c>
       <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>Same session opened by step 37.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>Feedback &amp; testimonial</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>Positive outcome (NPS)</t>
-        </is>
-      </c>
-      <c r="D41" s="10" t="inlineStr">
-        <is>
-          <t>TEMPLATE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>treatment_feedback_nps_survey</t>
-        </is>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>MARKETING</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>Hi {{1}}, thank you for trusting Gokavi Hospital with your care. On a scale of 0-10, how likely are you to recommend us to someone on a similar journey? Just reply with a number.</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>Quick Reply: 'Stop promotional messages' (Meta opt-out requirement for Marketing templates)</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
-        <is>
-          <t>CONFIRMED WITH USER: classified Marketing, not Utility. Sent proactively, well outside any open session, and is a satisfaction/NPS survey — Meta's own template guidelines list 'invitations to fill out a survey' as a Marketing example. Marketing templates cost more, are subject to Meta's marketing message-limit tiers, and need an opt-out affordance (added a Quick Reply button) — verify Meta's current opt-out requirement at submission time, as policy has changed before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Feedback &amp; testimonial</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Negative outcome</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>SESSION_REPLY</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="inlineStr">
-        <is>
-          <t>...Would you be open to sharing a few thoughts?</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>Yes I'll share / Not right now</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>Branch reply triggered immediately by the patient's low NPS score in step 40 — inside the session that step 40's template opened.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Feedback &amp; testimonial</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Testimonial ask</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>SESSION_REPLY</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
-        <is>
-          <t>...would you be open to sharing your story as a testimonial to help other patients considering treatment?</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr">
-        <is>
-          <t>Yes, happy to / No thanks</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
         <is>
           <t>Branch reply triggered immediately by the patient's high NPS score in step 40 — same session.</t>
         </is>
@@ -3915,4 +3727,326 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>What Changed</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Onboarding step count</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>10 steps -&gt; 5 questions + 1 closing message (6 rows total, was 10). Net document step count: 42 -&gt; 39.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>New: Language question</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Added as the very first question (before consent) — English / Kannada. Was not present in the previous version of this document at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Reworded/moved: City -&gt; Place</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>The old 'City' question (previously asked after Reason and Prior attempts) is now 'Place', asked immediately after Name — 3rd question overall, not 6th.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>New: Presenting problem (10-option list)</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Replaces BOTH the old 'Reason' question (3 options) and the old 'Prior attempts' question (3 options) with one fixed 10-option list: Infertility, Low sperm count, Zero sperm count (Azoospermia), Fibroid, Ovarian cyst, Endometriosis, Heavy bleeding, Painful periods, PCOS/PCOD, Irregular periods.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Removed: Patient ID / ID entry</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>The self-service 'do you have a patient ID' + free-text ID entry steps are gone. Returning-patient linking is now a staff/admin-panel task, not a WhatsApp self-service step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Removed: Partner link / Partner phone</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Dropped entirely — no longer asked during onboarding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Changed: What happens after onboarding</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Previously, finishing onboarding immediately opened the Booking section (Department -&gt; Doctor -&gt; Week -&gt; Date -&gt; Time). Now onboarding ends with a closing message ('Thank you! Our clinic will connect with you shortly.') and does NOT enter booking. Staff book manually. The Booking section further down in this sheet is unchanged in itself but is no longer auto-triggered from onboarding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Removed steps — detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Patient ID ("Do you already have a patient ID from the clinic?")</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Not in the client's 5-question list. Returning-patient record linking is now handled by clinic staff from the admin panel, not self-service over WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>ID entry (if Enter tapped) ("Please type your patient ID.")</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Removed along with the Patient ID question above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Partner link ("Add a partner/spouse contact for shared updates?")</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Not in the client's 5-question list. Dropped entirely from onboarding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Partner phone (if Yes) ("Please share your partner's WhatsApp number...")</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Removed along with the Partner link question above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Reason ("What brings you to us?" — IVF treatment / General consultation / Other)</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>Replaced by the new "Presenting problem" 10-option list (new step 6), which is more specific and clinically useful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Prior attempts ("Have you tried IVF or fertility treatment before?")</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Not in the client's 5-question list. Removed; not replaced by anything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Template impact check (2026-09)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Template Name</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Wording Affected?</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>art_act_consent_reminder</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>No wording change needed</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (appointment date) — no onboarding content (name/place/problem/patient ID) is quoted or implied in the approved wording. PROCESS NOTE (not a wording issue): this template's real-world trigger assumed booking happened right after onboarding. Since onboarding no longer books automatically, confirm with the clinic when/how this now gets sent (e.g. once staff manually create the appointment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>report_ready_verify_dob</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (name) and {{2}} (test name) plus a DOB security check — no onboarding-field dependency at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>careplan_ready_verify_dob</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (name) and {{2}} (doctor name) plus a DOB security check — no onboarding-field dependency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>post_opu_checkin_pain</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (name) and {{2}} (procedure date) — no onboarding-field dependency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>post_transfer_checkin_pain</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (name) and {{2}} (procedure date) — no onboarding-field dependency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>treatment_feedback_nps_survey</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>No change needed</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Body only references {{1}} (name) — no onboarding-field dependency.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>